--- a/docs/StructureDefinition-biobank-location.xlsx
+++ b/docs/StructureDefinition-biobank-location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-biobank-location.xlsx
+++ b/docs/StructureDefinition-biobank-location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/biobank-location</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/biobank-location</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -850,62 +853,64 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -958,123 +963,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1082,10 +1087,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1097,7 +1102,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1154,19 +1159,19 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1174,10 +1179,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1185,10 +1190,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1200,13 +1205,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1257,13 +1262,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1272,15 +1277,15 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1288,10 +1293,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1303,13 +1308,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1348,31 +1353,31 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1380,26 +1385,26 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>20</v>
@@ -1408,13 +1413,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1465,19 +1470,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1485,10 +1490,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1496,10 +1501,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1511,13 +1516,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1568,13 +1573,13 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
@@ -1583,15 +1588,15 @@
         <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1599,10 +1604,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1614,13 +1619,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1659,31 +1664,31 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1691,10 +1696,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1702,10 +1707,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1717,16 +1722,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1734,7 +1739,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1776,13 +1781,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1791,15 +1796,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1807,10 +1812,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1822,13 +1827,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1879,46 +1884,46 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -1927,13 +1932,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1984,19 +1989,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2004,10 +2009,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2015,10 +2020,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2030,13 +2035,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2087,13 +2092,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -2102,15 +2107,15 @@
         <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2118,10 +2123,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2133,13 +2138,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2178,31 +2183,31 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2221,10 +2226,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2236,16 +2241,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2253,7 +2258,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2295,13 +2300,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2310,15 +2315,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2326,10 +2331,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2341,13 +2346,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2398,30 +2403,30 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2429,10 +2434,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2444,13 +2449,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2501,13 +2506,13 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -2516,26 +2521,26 @@
         <v>20</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2547,16 +2552,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2594,42 +2599,42 @@
         <v>20</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2637,10 +2642,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2649,22 +2654,22 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -2713,30 +2718,30 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2744,38 +2749,38 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q18" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>20</v>
@@ -2796,13 +2801,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -2820,30 +2825,30 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2851,10 +2856,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2863,20 +2868,20 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -2925,30 +2930,30 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2956,10 +2961,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2968,20 +2973,20 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -2991,7 +2996,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -3030,30 +3035,30 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3061,10 +3066,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3073,22 +3078,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3098,7 +3103,7 @@
         <v>20</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>20</v>
@@ -3137,46 +3142,46 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3185,13 +3190,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3242,19 +3247,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3262,10 +3267,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3273,10 +3278,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3288,13 +3293,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3345,13 +3350,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -3360,15 +3365,15 @@
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3376,10 +3381,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3391,13 +3396,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3436,31 +3441,31 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -3468,10 +3473,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3479,10 +3484,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3494,16 +3499,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>20</v>
@@ -3553,13 +3558,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -3568,15 +3573,15 @@
         <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3584,10 +3589,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3599,13 +3604,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3656,30 +3661,30 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3687,10 +3692,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -3702,16 +3707,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3761,13 +3766,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -3776,15 +3781,15 @@
         <v>20</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3792,10 +3797,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -3807,13 +3812,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3864,22 +3869,22 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
